--- a/assets/excel/2026_5-1-2.xlsx
+++ b/assets/excel/2026_5-1-2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDAC2CE-14AE-452E-A80B-3956D7DA8F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6808149-CE2A-4C70-B650-8EE44730C5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
+    <workbookView xWindow="30360" yWindow="1425" windowWidth="21600" windowHeight="16575" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="29">
   <si>
     <t>Indikator 5.1.2: Erwerbsquote, Erwerbstätigenquote und Erwerbslosenanteil nach Zuwanderungsgeschichte</t>
   </si>
@@ -140,18 +140,6 @@
     <t xml:space="preserve">Frauen </t>
   </si>
   <si>
-    <t xml:space="preserve">1) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe. Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren. </t>
-  </si>
-  <si>
-    <t>2) Bezogen auf die Bevölkerung im Erwerbsalter (15 bis unter 65 Jahre).</t>
-  </si>
-  <si>
-    <t>3) Seit dem Jahr 2018 wird im Mikrozensus der Migrationshintergrund im weiteren Sinne jährlich berichtet. Durch eine rückwirkende Revision der Mikrozensusdaten wird auch für das Jahr 2017 der Migrationshintergrund im weiteren Sinne dargestellt. Die in der Tabelle ab dem Jahr 2017 berichteten Daten zum Migrationshintergrund entsprechen dem Migrationshintergrund im weiteren Sinne, bis 2016 wird der Migrationshintergrund im engeren Sinne abgebildet. Die Vergleichbarkeit zwischen den Jahren sowie für das Berichtsjahr 2017 zwischen den Berichten des Integrationsmonitoring Niedersachsen 2018 und 2019 ist dadurch eingeschränkt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4) Die Ergebnisse des Mikrozensus 2020 sind unter anderem aufgrund methodischer Effekte im Rahmen einer Neugestaltung der Erhebung sowie insbesondere aufgrund der Folgen der Corona-Pandemie in Ihrer Datenqualität eingeschränkt. Auf die Verwendung dieser Ergebnisse wird daher verzichtet. Weitere Informationen zur methodischen Neugestaltung des Mikrozensus ab 2020 und zu den Auswirkungen der Neugestaltung und der Corona-Krise auf die Ergebnisse des Jahres 2020 finden Sie auf der Informationsseite des Statistischen Bundesamtes: </t>
-  </si>
-  <si>
     <t>https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Haushalte-Familien/Methoden/mikrozensus-2020.html</t>
   </si>
   <si>
@@ -170,7 +158,22 @@
     <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
   </si>
   <si>
-    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                     </t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>1) Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
+  </si>
+  <si>
+    <t>2) Ohne Abschluss einschließlich Abschluss Förderschule</t>
+  </si>
+  <si>
+    <t>3) Seit dem Jahr 2018 wird im Mikrozensus der Migrationshintergrund im weiteren Sinne jährlich berichtet. Die in der Tabelle ab dem Jahr 2018 abgebildeten Daten zum Migrationshintergrund entsprechen dem Migrationshintergrund im weiteren Sinne, bis 2017 wird der Migrationshintergrund im engeren Sinne abgebildet. Die Vergleichbarkeit ist dadurch eingeschränkt.</t>
+  </si>
+  <si>
+    <t>4) Die Ergebnisse des Mikrozensus 2020 sind unter anderem aufgrund methodischer Effekte im Rahmen einer Neugestaltung der Erhebung sowie insbesondere aufgrund der Folgen der Corona-Pandemie in Ihrer Datenqualität eingeschränkt. Auf die Verwendung dieser Ergebnisse wird daher verzichtet. Weitere Informationen zur methodischen Neugestaltung des Mikrozensus ab 2020 und zu den Auswirkungen der Neugestaltung und der Corona-Krise auf die Ergebnisse des Jahres 2020 finden Sie auf der Informationsseite des Statistischen Bundesamtes:</t>
+  </si>
+  <si>
+    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                                                        </t>
   </si>
 </sst>
 </file>
@@ -180,7 +183,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +239,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -387,7 +395,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -422,31 +430,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -455,6 +440,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -470,24 +470,42 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -508,9 +526,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -548,7 +566,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -654,7 +672,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -796,7 +814,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -823,22 +841,22 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
       <c r="M3" s="8"/>
     </row>
     <row r="4" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -858,126 +876,126 @@
       <c r="I5" s="10"/>
     </row>
     <row r="6" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24" t="s">
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="25"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="27"/>
     </row>
     <row r="7" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="31"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26" t="s">
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26" t="s">
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="35"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="18"/>
     </row>
     <row r="8" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="31"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="36" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="36" t="s">
+      <c r="H8" s="22"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="24"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="36" t="s">
+      <c r="M8" s="22"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="37" t="s">
+      <c r="P8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="24" t="s">
+      <c r="Q8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="25"/>
+      <c r="R8" s="27"/>
     </row>
     <row r="9" spans="2:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="31"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="38"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="38"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="21"/>
       <c r="L9" s="11" t="s">
         <v>12</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N9" s="28"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="38"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="21"/>
       <c r="Q9" s="11" t="s">
         <v>12</v>
       </c>
@@ -986,25 +1004,25 @@
       </c>
     </row>
     <row r="10" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="24" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="25"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="27"/>
     </row>
     <row r="11" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="13">
@@ -3490,63 +3508,47 @@
       </c>
       <c r="S56" s="3"/>
     </row>
-    <row r="57" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="2"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-    </row>
-    <row r="58" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="15"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="2:19" s="18" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="33"/>
-    </row>
-    <row r="60" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B60" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D57" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="29"/>
+      <c r="D58" s="28"/>
+    </row>
+    <row r="59" spans="2:19" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+    </row>
+    <row r="60" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="32"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+    </row>
+    <row r="61" spans="2:19" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="34" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C61" s="34"/>
       <c r="D61" s="34"/>
@@ -3557,10 +3559,15 @@
       <c r="I61" s="34"/>
       <c r="J61" s="34"/>
       <c r="K61" s="34"/>
-    </row>
-    <row r="62" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L61" s="34"/>
+      <c r="M61" s="34"/>
+      <c r="N61" s="34"/>
+      <c r="O61" s="34"/>
+      <c r="P61" s="34"/>
+    </row>
+    <row r="62" spans="2:19" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="34" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C62" s="34"/>
       <c r="D62" s="34"/>
@@ -3571,119 +3578,69 @@
       <c r="I62" s="34"/>
       <c r="J62" s="34"/>
       <c r="K62" s="34"/>
-    </row>
-    <row r="63" spans="2:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="19" t="s">
+      <c r="L62" s="34"/>
+      <c r="M62" s="34"/>
+      <c r="N62" s="34"/>
+      <c r="O62" s="34"/>
+      <c r="P62" s="34"/>
+    </row>
+    <row r="63" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="36"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+    </row>
+    <row r="64" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+    </row>
+    <row r="65" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="38"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+    </row>
+    <row r="66" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D66" s="28"/>
+    </row>
+    <row r="67" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="28"/>
+    </row>
+    <row r="68" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="28"/>
+    </row>
+    <row r="69" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="28"/>
+    </row>
+    <row r="70" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-    </row>
-    <row r="64" spans="2:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-    </row>
-    <row r="65" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-    </row>
-    <row r="66" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="22"/>
-      <c r="K67" s="22"/>
-    </row>
-    <row r="68" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-    </row>
-    <row r="69" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="22"/>
-    </row>
-    <row r="70" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
+      <c r="D70" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B59:K59"/>
-    <mergeCell ref="B61:K61"/>
-    <mergeCell ref="B62:K62"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
@@ -3696,10 +3653,23 @@
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:M7"/>
     <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="B61:P61"/>
+    <mergeCell ref="B62:P62"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B70" r:id="rId1" xr:uid="{3ECA3C8E-D001-4E48-A48D-3E856F57D422}"/>
-    <hyperlink ref="B63" r:id="rId2" xr:uid="{F46E98A5-C820-48A7-8055-0E550FAC5AAD}"/>
+    <hyperlink ref="B70" r:id="rId1" xr:uid="{80329408-6641-481A-B447-F264B7A3543D}"/>
+    <hyperlink ref="B63" r:id="rId2" xr:uid="{6F9ADE31-0F8C-4F93-95FE-711EA199C706}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/excel/2026_5-1-2.xlsx
+++ b/assets/excel/2026_5-1-2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BiesterChristophLSN\Desktop\MZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784EAAA1-CD3C-44F2-B823-7F0E24E73403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6808149-CE2A-4C70-B650-8EE44730C5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20052" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
+    <workbookView xWindow="30360" yWindow="1425" windowWidth="21600" windowHeight="16575" xr2:uid="{4424B46B-A95E-48DA-B113-8E8F86BF46C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="29">
   <si>
     <t>Indikator 5.1.2: Erwerbsquote, Erwerbstätigenquote und Erwerbslosenanteil nach Zuwanderungsgeschichte</t>
   </si>
@@ -140,15 +140,6 @@
     <t xml:space="preserve">Frauen </t>
   </si>
   <si>
-    <t>2) Bezogen auf die Bevölkerung im Erwerbsalter (15 bis unter 65 Jahre).</t>
-  </si>
-  <si>
-    <t>3) Seit dem Jahr 2018 wird im Mikrozensus der Migrationshintergrund im weiteren Sinne jährlich berichtet. Durch eine rückwirkende Revision der Mikrozensusdaten wird auch für das Jahr 2017 der Migrationshintergrund im weiteren Sinne dargestellt. Die in der Tabelle ab dem Jahr 2017 berichteten Daten zum Migrationshintergrund entsprechen dem Migrationshintergrund im weiteren Sinne, bis 2016 wird der Migrationshintergrund im engeren Sinne abgebildet. Die Vergleichbarkeit zwischen den Jahren sowie für das Berichtsjahr 2017 zwischen den Berichten des Integrationsmonitoring Niedersachsen 2018 und 2019 ist dadurch eingeschränkt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4) Die Ergebnisse des Mikrozensus 2020 sind unter anderem aufgrund methodischer Effekte im Rahmen einer Neugestaltung der Erhebung sowie insbesondere aufgrund der Folgen der Corona-Pandemie in Ihrer Datenqualität eingeschränkt. Auf die Verwendung dieser Ergebnisse wird daher verzichtet. Weitere Informationen zur methodischen Neugestaltung des Mikrozensus ab 2020 und zu den Auswirkungen der Neugestaltung und der Corona-Krise auf die Ergebnisse des Jahres 2020 finden Sie auf der Informationsseite des Statistischen Bundesamtes: </t>
-  </si>
-  <si>
     <t>https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Haushalte-Familien/Methoden/mikrozensus-2020.html</t>
   </si>
   <si>
@@ -167,10 +158,22 @@
     <t>Migration und Teilhabe in Niedersachsen - Integrationsmonitoring 2026</t>
   </si>
   <si>
-    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                     </t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">1)  Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren. </t>
+    <t>1) Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
+  </si>
+  <si>
+    <t>2) Ohne Abschluss einschließlich Abschluss Förderschule</t>
+  </si>
+  <si>
+    <t>3) Seit dem Jahr 2018 wird im Mikrozensus der Migrationshintergrund im weiteren Sinne jährlich berichtet. Die in der Tabelle ab dem Jahr 2018 abgebildeten Daten zum Migrationshintergrund entsprechen dem Migrationshintergrund im weiteren Sinne, bis 2017 wird der Migrationshintergrund im engeren Sinne abgebildet. Die Vergleichbarkeit ist dadurch eingeschränkt.</t>
+  </si>
+  <si>
+    <t>4) Die Ergebnisse des Mikrozensus 2020 sind unter anderem aufgrund methodischer Effekte im Rahmen einer Neugestaltung der Erhebung sowie insbesondere aufgrund der Folgen der Corona-Pandemie in Ihrer Datenqualität eingeschränkt. Auf die Verwendung dieser Ergebnisse wird daher verzichtet. Weitere Informationen zur methodischen Neugestaltung des Mikrozensus ab 2020 und zu den Auswirkungen der Neugestaltung und der Corona-Krise auf die Ergebnisse des Jahres 2020 finden Sie auf der Informationsseite des Statistischen Bundesamtes:</t>
+  </si>
+  <si>
+    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                                                        </t>
   </si>
 </sst>
 </file>
@@ -180,7 +183,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +239,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -387,7 +395,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -422,31 +430,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -488,6 +473,39 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -823,22 +841,22 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
       <c r="M3" s="8"/>
     </row>
     <row r="4" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -858,126 +876,126 @@
       <c r="I5" s="10"/>
     </row>
     <row r="6" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33" t="s">
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="38"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="27"/>
     </row>
     <row r="7" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="36"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26" t="s">
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26" t="s">
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="29"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="18"/>
     </row>
     <row r="8" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="30" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="30" t="s">
+      <c r="H8" s="22"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="K8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="33" t="s">
+      <c r="L8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="33"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="30" t="s">
+      <c r="M8" s="22"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="31" t="s">
+      <c r="P8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="33" t="s">
+      <c r="Q8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="38"/>
+      <c r="R8" s="27"/>
     </row>
     <row r="9" spans="2:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="36"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="32"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="32"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="21"/>
       <c r="L9" s="11" t="s">
         <v>12</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N9" s="28"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="32"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="21"/>
       <c r="Q9" s="11" t="s">
         <v>12</v>
       </c>
@@ -986,25 +1004,25 @@
       </c>
     </row>
     <row r="10" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="37"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="33" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="38"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="27"/>
     </row>
     <row r="11" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="13">
@@ -3490,184 +3508,136 @@
       </c>
       <c r="S56" s="3"/>
     </row>
-    <row r="57" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="2"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-    </row>
-    <row r="58" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="15"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="2:19" s="18" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="24" t="s">
+    <row r="57" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D57" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="29"/>
+      <c r="D58" s="28"/>
+    </row>
+    <row r="59" spans="2:19" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+    </row>
+    <row r="60" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="32"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+    </row>
+    <row r="61" spans="2:19" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
+      <c r="L61" s="34"/>
+      <c r="M61" s="34"/>
+      <c r="N61" s="34"/>
+      <c r="O61" s="34"/>
+      <c r="P61" s="34"/>
+    </row>
+    <row r="62" spans="2:19" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="24"/>
-      <c r="K59" s="24"/>
-    </row>
-    <row r="60" spans="2:19" s="5" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B60" s="16" t="s">
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="34"/>
+      <c r="M62" s="34"/>
+      <c r="N62" s="34"/>
+      <c r="O62" s="34"/>
+      <c r="P62" s="34"/>
+    </row>
+    <row r="63" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="25" t="s">
+      <c r="C63" s="36"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+    </row>
+    <row r="64" spans="2:19" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+    </row>
+    <row r="65" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-      <c r="J61" s="25"/>
-      <c r="K61" s="25"/>
-    </row>
-    <row r="62" spans="2:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="25" t="s">
+      <c r="C65" s="38"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+    </row>
+    <row r="66" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D66" s="28"/>
+    </row>
+    <row r="67" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="25"/>
-      <c r="J62" s="25"/>
-      <c r="K62" s="25"/>
-    </row>
-    <row r="63" spans="2:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="19" t="s">
+      <c r="D67" s="28"/>
+    </row>
+    <row r="68" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="28"/>
+    </row>
+    <row r="69" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-    </row>
-    <row r="64" spans="2:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-    </row>
-    <row r="65" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="21" t="s">
+      <c r="D69" s="28"/>
+    </row>
+    <row r="70" spans="2:7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-    </row>
-    <row r="66" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="22"/>
-      <c r="K67" s="22"/>
-    </row>
-    <row r="68" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-    </row>
-    <row r="69" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="22"/>
-    </row>
-    <row r="70" spans="2:11" s="18" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
+      <c r="D70" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3683,9 +3653,6 @@
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="J7:M7"/>
     <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="B59:K59"/>
-    <mergeCell ref="B61:K61"/>
-    <mergeCell ref="B62:K62"/>
     <mergeCell ref="N7:N9"/>
     <mergeCell ref="O7:R7"/>
     <mergeCell ref="E8:E9"/>
@@ -3696,10 +3663,13 @@
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="P8:P9"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="B61:P61"/>
+    <mergeCell ref="B62:P62"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B70" r:id="rId1" xr:uid="{3ECA3C8E-D001-4E48-A48D-3E856F57D422}"/>
-    <hyperlink ref="B63" r:id="rId2" xr:uid="{F46E98A5-C820-48A7-8055-0E550FAC5AAD}"/>
+    <hyperlink ref="B70" r:id="rId1" xr:uid="{80329408-6641-481A-B447-F264B7A3543D}"/>
+    <hyperlink ref="B63" r:id="rId2" xr:uid="{6F9ADE31-0F8C-4F93-95FE-711EA199C706}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
